--- a/reports/livrables/L4_analyse/q5_tableaux.xlsx
+++ b/reports/livrables/L4_analyse/q5_tableaux.xlsx
@@ -1,38 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_calendrier" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_niveaux_par_exercice" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_unites_remisees" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_canaux" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_canaux_evolution" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_cout_des_remises" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_remises_par_magasin" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4_correlations" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5_avec_sans_par_canal" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5_avec_sans_par_exercice" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5_verification_constat_06" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5_robustesse_magasins" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5_robustesse_hors_magasins" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5_taille_des_lignes" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6_canal_et_niveau" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6_niveau_par_exercice" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6_par_niveau_produits" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7_remises_par_gamme" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7_remises_par_age" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7_taux_effectif_canal_gamme" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7_decomposition_taux_effectif" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7_par_segment" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8_contribution" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8_leviers" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8_levier_repris_dans_06" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9_registre_des_tests" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="2_calendrier" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="2_niveaux_par_exercice" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="2_unites_remisees" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="2_canaux" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="2_canaux_evolution" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="3_cout_des_remises" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="3_remises_par_magasin" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="4_correlations" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="5_avec_sans_par_canal" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="5_avec_sans_par_exercice" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="5_verification_constat_06" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="5_robustesse_magasins" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="5_robustesse_hors_magasins" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="5_taille_des_lignes" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="6_canal_et_niveau" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="6_niveau_par_exercice" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="6_par_niveau_produits" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="7_remises_par_gamme" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="7_remises_par_age" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="7_taux_effectif_canal_gamme" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="7_decomposition_taux_effectif" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="7_par_segment" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="8_contribution" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="8_leviers" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="8_levier_repris_dans_06" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="9_registre_des_tests" sheetId="26" state="visible" r:id="rId26"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
